--- a/docs/big-oppy-decoder-truthtable.xlsx
+++ b/docs/big-oppy-decoder-truthtable.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="method" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="truth_table" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="class_summary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="gate_fit" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,7 +442,6 @@
           <t>decoder pixel-class truth table</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -7580,4 +7580,685 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C63"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>decoder pixel-class gate fit (P2) — greedy tree, &lt;=5 dispatch-time variables, leave-one-CLIP-out validation</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>VERDICT</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>9-way fine classes</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>REFUSED: train 0.922 vs LOCO-CV 0.157 — ~2 clips/class cannot support a 9-way gate (gate_refit law 3: fitting on one point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>4-way cost tiers</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>SUPPORTED: train 1.000, LOCO-CV 0.804 over 51 rows / 17 clip-folds</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>superclasses</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ENTROPY-EXTREME={grain}  DENSE-INTER={fastmotion,detail,pan,complex}  MID={medium,smooth}  LIGHT={screen,static}</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>caveat</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>valid on varied axes only: class x tier x resolution, qp26, x264 provenance. NOT validated across qp/bitrate/other encoders</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>selected variables, 4-way gate (order of first use)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>entropy_calls_per_mb</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>2</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>mb_skip_frac</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>3</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>bits_per_mb</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>4</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>skiprecon_calls_per_mb</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>5</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>dequant_calls_per_mb</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>4-way decision tree (thresholds)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>entropy_calls_per_mb &lt;= 2.565?</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  mb_skip_frac &lt;= 0.157?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    -&gt; MID</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  mb_skip_frac &gt; 0.157:</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    -&gt; LIGHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>entropy_calls_per_mb &gt; 2.565:</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  bits_per_mb &lt;= 363.665?</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    skiprecon_calls_per_mb &lt;= 0.494?</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      dequant_calls_per_mb &lt;= 1.92?</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        -&gt; MID</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      dequant_calls_per_mb &gt; 1.92:</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        -&gt; DENSE-INTER</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    skiprecon_calls_per_mb &gt; 0.494:</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      -&gt; MID</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  bits_per_mb &gt; 363.665:</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    -&gt; ENTROPY-EXTREME</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>single-feature ranking (4-way)</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>info gain</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>1-feature acc</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>entropy_calls_per_mb</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>0.7433999999999999</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.922</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>dequant_calls_per_mb</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>0.6589</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>bits_per_mb</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>0.5832000000000001</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.961</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>mb_intra_frac</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>0.5226</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.922</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>skiprecon_calls_per_mb</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>0.5226</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.922</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>intra_calls_per_mb</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>0.432</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.804</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>mb_skip_frac</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.922</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>mb_p_frac</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>0.3591</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.765</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>mc_calls_per_mb</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>0.2886</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.824</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>mbs_per_frame</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>0.1539</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0.471</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>mb_b_frac</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>0.0431</v>
+      </c>
+      <c r="C45" t="n">
+        <v>0.569</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>is_cabac</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" t="n">
+        <v>0.471</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>4-way CV confusion: true</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>correct/total</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>misses</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>DENSE-INTER</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>23/24</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>{'MID': 1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>ENTROPY-EXTREME</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>4/6</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>{'DENSE-INTER': 2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>LIGHT</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>9/12</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>{'MID': 2, 'DENSE-INTER': 1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>5/9</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>{'LIGHT': 2, 'DENSE-INTER': 2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>9-way CV confusion (the refusal evidence): true</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>correct/total</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>misses</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>complex</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>0/6</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>{'screen': 1, 'pan': 4, 'detail': 1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>detail</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>0/6</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>{'complex': 2, 'pan': 2, 'fastmotion': 2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>fastmotion</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>0/6</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>{'pan': 5, 'complex': 1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>grain</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>6/6</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2/6</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>{'complex': 2, 'detail': 1, 'static': 1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>pan</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>0/6</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>{'complex': 4, 'detail': 2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>screen</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>0/6</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>{'static': 3, 'complex': 1, 'medium': 2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>smooth</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>0/3</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>{'medium': 1, 'screen': 2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>static</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>0/6</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>{'screen': 6}</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/big-oppy-decoder-truthtable.xlsx
+++ b/docs/big-oppy-decoder-truthtable.xlsx
@@ -7588,7 +7588,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C63"/>
+  <dimension ref="A1:C69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -8171,7 +8171,6 @@
           <t>6/6</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -8255,6 +8254,61 @@
       <c r="C63" t="inlineStr">
         <is>
           <t>{'screen': 6}</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="inlineStr">
+        <is>
+          <t>PER-TIER FIT (are the fittings identical across tool tiers?)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>verdict</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>variables + tree SHAPE tier-stable; THRESHOLDS are not — root entropy_calls_per_mb: cavlc 5.575 / main 3.575 / high 2.335 (2.4x swing; the feature measures different call structures per coder). bits_per_mb split: 406.7 / 315.4 / 340.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>pooled tree CV by tier</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>cavlc 0.882, main 0.765, high 0.765 — pooled is a fair compromise, but wiring should use PER-TIER thresholds behind GATE 0 (tool tier routes first anyway)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>per-tier independent fits</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>cavlc train 1.000 CV 0.824; main train 1.000 CV 0.765; high train 1.000 CV 0.765 (17 rows each — small-N, verdict rests on 17 clip-folds)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>DATA DEFECT (found via impossible number)</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>mb_skip_frac median 0.948 on cavlc tier: dec-mb-P/B scopes exist only in the CABAC loop, so mb_p_frac/mb_b_frac read 0 and skip_frac ~= 1 - intra on ALL cavlc rows. mb_p/b/skip fracs are INVALID on the cavlc tier; pooled tree survives because cavlc routes on entropy_calls first. Fix: add CAVLC-loop MB scopes before wiring skip_frac into any cavlc-tier gate</t>
         </is>
       </c>
     </row>

--- a/docs/big-oppy-decoder-truthtable.xlsx
+++ b/docs/big-oppy-decoder-truthtable.xlsx
@@ -11,6 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="truth_table" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="class_summary" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="gate_fit" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="gate_fit_per_tier" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -8315,4 +8316,1051 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C96"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="90" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>GATE 1 — full per-tier fittings (4-way cost-tier superclasses)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>method</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>same P2 fitter as gate_fit, run per tool tier; cavlc EXCLUDES mb_p/b/skip_frac (CABAC-only scopes — invalid columns on that tier); min-leaf 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>small-N notice</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>17 rows / 17 clip-folds per tier — each verdict rests on &lt;=6 clips per superclass; treat thresholds as v1, refit after qp sweep</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1">
+        <f>== CAVLC ===</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>train / LOCO-CV</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1.000 / 0.824 (17 rows, 17 folds)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>variables (order of first use)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>entropy_calls_per_mb, bits_per_mb</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>tree</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>entropy_calls_per_mb &lt;= 5.575?</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  entropy_calls_per_mb &lt;= 2.96?</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    -&gt; LIGHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  entropy_calls_per_mb &gt; 2.96:</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    -&gt; MID</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>entropy_calls_per_mb &gt; 5.575:</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  bits_per_mb &lt;= 406.65?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    -&gt; DENSE-INTER</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  bits_per_mb &gt; 406.65:</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    -&gt; ENTROPY-EXTREME</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>single-feature ranking</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>info gain</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>1-feature acc</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>entropy_calls_per_mb</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0.9774</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>dequant_calls_per_mb</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0.9774</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.9409999999999999</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>skiprecon_calls_per_mb</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0.9774</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>mc_calls_per_mb</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>0.8355</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>bits_per_mb</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>0.7458</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.9409999999999999</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>mb_intra_frac</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>0.5226</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.824</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>intra_calls_per_mb</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>0.4165</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.706</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>mbs_per_frame</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>0.1539</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.471</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>CV confusion: true</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>correct/total</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>misses</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>DENSE-INTER</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>7/8</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>{'MID': 1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>ENTROPY-EXTREME</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2/2</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>LIGHT</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>3/4</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>{'DENSE-INTER': 1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2/3</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>{'DENSE-INTER': 1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1">
+        <f>== MAIN ===</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>train / LOCO-CV</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>1.000 / 0.765 (17 rows, 17 folds)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>variables (order of first use)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>entropy_calls_per_mb, skiprecon_calls_per_mb, bits_per_mb</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>tree</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>entropy_calls_per_mb &lt;= 3.575?</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  skiprecon_calls_per_mb &lt;= 0.32?</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    -&gt; MID</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  skiprecon_calls_per_mb &gt; 0.32:</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    -&gt; LIGHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>entropy_calls_per_mb &gt; 3.575:</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  bits_per_mb &lt;= 315.43?</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    -&gt; DENSE-INTER</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  bits_per_mb &gt; 315.43:</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    -&gt; ENTROPY-EXTREME</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>single-feature ranking</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>info gain</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>1-feature acc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>entropy_calls_per_mb</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>0.9774</v>
+      </c>
+      <c r="C49" t="n">
+        <v>0.9409999999999999</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>dequant_calls_per_mb</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>0.9774</v>
+      </c>
+      <c r="C50" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>mb_p_frac</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>0.9367</v>
+      </c>
+      <c r="C51" t="n">
+        <v>0.882</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>skiprecon_calls_per_mb</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>0.7871</v>
+      </c>
+      <c r="C52" t="n">
+        <v>0.9409999999999999</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>mb_skip_frac</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>0.7871</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0.882</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>bits_per_mb</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>0.5283</v>
+      </c>
+      <c r="C54" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>mb_intra_frac</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>0.5226</v>
+      </c>
+      <c r="C55" t="n">
+        <v>0.882</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>intra_calls_per_mb</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>0.5226</v>
+      </c>
+      <c r="C56" t="n">
+        <v>0.824</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>mc_calls_per_mb</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>0.3165</v>
+      </c>
+      <c r="C57" t="n">
+        <v>0.882</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>mb_b_frac</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>0.2271</v>
+      </c>
+      <c r="C58" t="n">
+        <v>0.647</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>mbs_per_frame</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>0.1539</v>
+      </c>
+      <c r="C59" t="n">
+        <v>0.471</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>CV confusion: true</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>correct/total</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>misses</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>DENSE-INTER</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>8/8</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>ENTROPY-EXTREME</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2/2</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>LIGHT</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>3/4</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>{'MID': 1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>0/3</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>{'LIGHT': 3}</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1">
+        <f>== HIGH ===</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>train / LOCO-CV</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>1.000 / 0.824 (17 rows, 17 folds)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>variables (order of first use)</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>entropy_calls_per_mb, skiprecon_calls_per_mb, bits_per_mb</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="inlineStr">
+        <is>
+          <t>tree</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>entropy_calls_per_mb &lt;= 2.335?</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  skiprecon_calls_per_mb &lt;= 0.3575?</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    -&gt; MID</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  skiprecon_calls_per_mb &gt; 0.3575:</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    -&gt; LIGHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>entropy_calls_per_mb &gt; 2.335:</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  bits_per_mb &lt;= 340.11?</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    -&gt; DENSE-INTER</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  bits_per_mb &gt; 340.11:</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    -&gt; ENTROPY-EXTREME</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>single-feature ranking</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>info gain</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>1-feature acc</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>entropy_calls_per_mb</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>0.9774</v>
+      </c>
+      <c r="C81" t="n">
+        <v>0.9409999999999999</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>dequant_calls_per_mb</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>0.9774</v>
+      </c>
+      <c r="C82" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>mb_p_frac</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>0.8355</v>
+      </c>
+      <c r="C83" t="n">
+        <v>0.9409999999999999</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>skiprecon_calls_per_mb</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>0.7871</v>
+      </c>
+      <c r="C84" t="n">
+        <v>0.9409999999999999</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>mb_skip_frac</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>0.7871</v>
+      </c>
+      <c r="C85" t="n">
+        <v>0.9409999999999999</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>bits_per_mb</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>0.7458</v>
+      </c>
+      <c r="C86" t="n">
+        <v>0.9409999999999999</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>intra_calls_per_mb</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>0.6157</v>
+      </c>
+      <c r="C87" t="n">
+        <v>0.9409999999999999</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>mb_intra_frac</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>0.5283</v>
+      </c>
+      <c r="C88" t="n">
+        <v>0.824</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>mc_calls_per_mb</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>0.5102</v>
+      </c>
+      <c r="C89" t="n">
+        <v>0.706</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>mb_b_frac</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>0.2857</v>
+      </c>
+      <c r="C90" t="n">
+        <v>0.647</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>mbs_per_frame</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>0.1539</v>
+      </c>
+      <c r="C91" t="n">
+        <v>0.471</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="inlineStr">
+        <is>
+          <t>CV confusion: true</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>correct/total</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="inlineStr">
+        <is>
+          <t>misses</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>DENSE-INTER</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>8/8</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>ENTROPY-EXTREME</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2/2</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>LIGHT</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>3/4</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>{'DENSE-INTER': 1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>1/3</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>{'LIGHT': 1, 'DENSE-INTER': 1}</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/big-oppy-decoder-truthtable.xlsx
+++ b/docs/big-oppy-decoder-truthtable.xlsx
@@ -12,6 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="class_summary" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="gate_fit" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="gate_fit_per_tier" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="main_vs_default" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -8636,7 +8637,6 @@
           <t>2/2</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -8967,7 +8967,6 @@
           <t>8/8</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -8980,7 +8979,6 @@
           <t>2/2</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -9311,7 +9309,6 @@
           <t>8/8</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -9324,7 +9321,6 @@
           <t>2/2</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -9357,6 +9353,5056 @@
       <c r="C96" t="inlineStr">
         <is>
           <t>{'LIGHT': 1, 'DENSE-INTER': 1}</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F199"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>MAIN (medium + Main profile) vs DEFAULT (x264 zero-flag toolset: medium + High, CABAC, 8x8, weightp; RATE PINNED at qp26 for axis isolation — true default is CRF23)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>conformance (default tier)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ALL IDENTICAL vs ffmpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>timing provenance</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>loaded box (faucet) — ordinal only. Counter columns deterministic.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>clip</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>class</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>MAIN</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>DEFAULT</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>delta_pct</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>720p50_shields_ter</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>detail</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>bits_per_mb</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>35.36</v>
+      </c>
+      <c r="E6" t="n">
+        <v>38.62</v>
+      </c>
+      <c r="F6" t="n">
+        <v>9.199999999999999</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>720p50_shields_ter</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>detail</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>entropy_calls_per_mb</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-28.2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>720p50_shields_ter</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>detail</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>skiprecon_calls_per_mb</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.082</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.082</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>720p50_shields_ter</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>detail</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>dequant_calls_per_mb</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-14.9</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>720p50_shields_ter</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>detail</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>mc_calls_per_mb</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="E10" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>720p50_shields_ter</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>detail</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>mb_intra_frac</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0.0373</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.0377</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>720p50_shields_ter</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>detail</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>share_entropy_pct</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="E12" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-14.7</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>720p50_shields_ter</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>detail</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>share_inter_mc_pct</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="E13" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-12.9</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>720p50_shields_ter</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>detail</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>share_deblock_pct</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>8</v>
+      </c>
+      <c r="E14" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>720p50_shields_ter</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>detail</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>ns_per_mb</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>1416.7</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1381.5</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-2.5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>720p5994_stockholm_ter</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>pan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>bits_per_mb</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>34.35</v>
+      </c>
+      <c r="E16" t="n">
+        <v>40.85</v>
+      </c>
+      <c r="F16" t="n">
+        <v>18.9</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>720p5994_stockholm_ter</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>pan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>entropy_calls_per_mb</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-31.1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>720p5994_stockholm_ter</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>pan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>skiprecon_calls_per_mb</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0.099</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.089</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-10.1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>720p5994_stockholm_ter</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>pan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>dequant_calls_per_mb</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-19</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>720p5994_stockholm_ter</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>pan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>mc_calls_per_mb</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="E20" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>720p5994_stockholm_ter</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>pan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>mb_intra_frac</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>0.0357</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.0367</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>720p5994_stockholm_ter</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>pan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>share_entropy_pct</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="E22" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-6.8</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>720p5994_stockholm_ter</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>pan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>share_inter_mc_pct</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="E23" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-5.7</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>720p5994_stockholm_ter</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>pan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>share_deblock_pct</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="E24" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-15.7</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>720p5994_stockholm_ter</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>pan</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>ns_per_mb</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>1335.2</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1386.6</v>
+      </c>
+      <c r="F25" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>FourPeople_1280x720_60</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>static</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>bits_per_mb</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="E26" t="n">
+        <v>9.02</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>FourPeople_1280x720_60</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>static</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>entropy_calls_per_mb</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-34.5</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>FourPeople_1280x720_60</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>static</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>skiprecon_calls_per_mb</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>FourPeople_1280x720_60</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>static</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>dequant_calls_per_mb</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="F29" t="n">
+        <v>-18.3</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>FourPeople_1280x720_60</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>static</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>mc_calls_per_mb</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="E30" t="n">
+        <v>5</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>FourPeople_1280x720_60</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>static</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>mb_intra_frac</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>0.0198</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.0198</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>FourPeople_1280x720_60</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>static</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>share_entropy_pct</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="E32" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="F32" t="n">
+        <v>-15.6</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>FourPeople_1280x720_60</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>static</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>share_inter_mc_pct</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="E33" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="F33" t="n">
+        <v>-2.8</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>FourPeople_1280x720_60</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>static</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>share_deblock_pct</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E34" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="F34" t="n">
+        <v>-6</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>FourPeople_1280x720_60</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>static</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>ns_per_mb</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>800.5</v>
+      </c>
+      <c r="E35" t="n">
+        <v>703.7</v>
+      </c>
+      <c r="F35" t="n">
+        <v>-12.1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>akiyo_cif</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>static</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>bits_per_mb</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>8.640000000000001</v>
+      </c>
+      <c r="E36" t="n">
+        <v>8.91</v>
+      </c>
+      <c r="F36" t="n">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>akiyo_cif</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>static</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>entropy_calls_per_mb</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="F37" t="n">
+        <v>-25</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>akiyo_cif</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>static</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>skiprecon_calls_per_mb</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>0.363</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.366</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>akiyo_cif</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>static</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>dequant_calls_per_mb</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="F39" t="n">
+        <v>-17.4</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>akiyo_cif</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>static</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>mc_calls_per_mb</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>5.31</v>
+      </c>
+      <c r="E40" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>akiyo_cif</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>static</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>mb_intra_frac</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>0.008500000000000001</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.008500000000000001</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>akiyo_cif</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>static</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>share_entropy_pct</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>10</v>
+      </c>
+      <c r="E42" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="F42" t="n">
+        <v>-14</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>akiyo_cif</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>static</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>share_inter_mc_pct</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="E43" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>akiyo_cif</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>static</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>share_deblock_pct</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E44" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="F44" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>akiyo_cif</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>static</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>ns_per_mb</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>795.5</v>
+      </c>
+      <c r="E45" t="n">
+        <v>688.1</v>
+      </c>
+      <c r="F45" t="n">
+        <v>-13.5</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>blue_sky_1080p25</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>smooth</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>bits_per_mb</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>20.42</v>
+      </c>
+      <c r="E46" t="n">
+        <v>20.86</v>
+      </c>
+      <c r="F46" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>blue_sky_1080p25</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>smooth</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>entropy_calls_per_mb</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="E47" t="n">
+        <v>2</v>
+      </c>
+      <c r="F47" t="n">
+        <v>-20.9</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>blue_sky_1080p25</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>smooth</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>skiprecon_calls_per_mb</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>0.304</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.302</v>
+      </c>
+      <c r="F48" t="n">
+        <v>-0.7</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>blue_sky_1080p25</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>smooth</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>dequant_calls_per_mb</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="E49" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="F49" t="n">
+        <v>-2.4</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>blue_sky_1080p25</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>smooth</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>mc_calls_per_mb</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="E50" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>blue_sky_1080p25</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>smooth</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>mb_intra_frac</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>0.0281</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.0299</v>
+      </c>
+      <c r="F51" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>blue_sky_1080p25</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>smooth</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>share_entropy_pct</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="E52" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="F52" t="n">
+        <v>-28</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>blue_sky_1080p25</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>smooth</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>share_inter_mc_pct</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="E53" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="F53" t="n">
+        <v>-2.2</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>blue_sky_1080p25</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>smooth</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>share_deblock_pct</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="E54" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="F54" t="n">
+        <v>-5.5</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>blue_sky_1080p25</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>smooth</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>ns_per_mb</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>1198.7</v>
+      </c>
+      <c r="E55" t="n">
+        <v>1153.6</v>
+      </c>
+      <c r="F55" t="n">
+        <v>-3.8</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>bus_cif</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>pan</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>bits_per_mb</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>103.61</v>
+      </c>
+      <c r="E56" t="n">
+        <v>106.52</v>
+      </c>
+      <c r="F56" t="n">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>bus_cif</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>pan</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>entropy_calls_per_mb</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>7.21</v>
+      </c>
+      <c r="E57" t="n">
+        <v>5</v>
+      </c>
+      <c r="F57" t="n">
+        <v>-30.7</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>bus_cif</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>pan</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>skiprecon_calls_per_mb</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>bus_cif</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>pan</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>dequant_calls_per_mb</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="E59" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="F59" t="n">
+        <v>-24.2</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>bus_cif</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>pan</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>mc_calls_per_mb</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="E60" t="n">
+        <v>6.64</v>
+      </c>
+      <c r="F60" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>bus_cif</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>pan</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>mb_intra_frac</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>0.0324</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0.0311</v>
+      </c>
+      <c r="F61" t="n">
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>bus_cif</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>pan</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>share_entropy_pct</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="E62" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="F62" t="n">
+        <v>-7.7</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>bus_cif</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>pan</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>share_inter_mc_pct</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="E63" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="F63" t="n">
+        <v>-9.5</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>bus_cif</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>pan</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>share_deblock_pct</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E64" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="F64" t="n">
+        <v>-13.8</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>bus_cif</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>pan</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>ns_per_mb</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>2420</v>
+      </c>
+      <c r="E65" t="n">
+        <v>2276.9</v>
+      </c>
+      <c r="F65" t="n">
+        <v>-5.9</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>crew_4cif</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>complex</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>bits_per_mb</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>34.41</v>
+      </c>
+      <c r="E66" t="n">
+        <v>36.64</v>
+      </c>
+      <c r="F66" t="n">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>crew_4cif</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>complex</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>entropy_calls_per_mb</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="E67" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="F67" t="n">
+        <v>-34.4</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>crew_4cif</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>complex</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>skiprecon_calls_per_mb</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>0.089</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="F68" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>crew_4cif</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>complex</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>dequant_calls_per_mb</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="E69" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="F69" t="n">
+        <v>-8.4</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>crew_4cif</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>complex</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>mc_calls_per_mb</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="E70" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="F70" t="n">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>crew_4cif</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>complex</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>mb_intra_frac</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>0.0521</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0.051</v>
+      </c>
+      <c r="F71" t="n">
+        <v>-2.1</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>crew_4cif</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>complex</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>share_entropy_pct</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="E72" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="F72" t="n">
+        <v>-26.3</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>crew_4cif</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>complex</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>share_inter_mc_pct</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="E73" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="F73" t="n">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>crew_4cif</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>complex</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>share_deblock_pct</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="E74" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="F74" t="n">
+        <v>-14</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>crew_4cif</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>complex</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>ns_per_mb</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>1372.6</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1416.8</v>
+      </c>
+      <c r="F75" t="n">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>crowd_run_1080p50</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>fastmotion</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>bits_per_mb</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>120.4</v>
+      </c>
+      <c r="E76" t="n">
+        <v>123.78</v>
+      </c>
+      <c r="F76" t="n">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>crowd_run_1080p50</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>fastmotion</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>entropy_calls_per_mb</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>9.02</v>
+      </c>
+      <c r="E77" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="F77" t="n">
+        <v>-23.5</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>crowd_run_1080p50</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>fastmotion</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>skiprecon_calls_per_mb</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>0.056</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="F78" t="n">
+        <v>-3.6</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>crowd_run_1080p50</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>fastmotion</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>dequant_calls_per_mb</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>5.82</v>
+      </c>
+      <c r="E79" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="F79" t="n">
+        <v>-19.4</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>crowd_run_1080p50</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>fastmotion</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>mc_calls_per_mb</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="E80" t="n">
+        <v>6.82</v>
+      </c>
+      <c r="F80" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>crowd_run_1080p50</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>fastmotion</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>mb_intra_frac</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>0.0638</v>
+      </c>
+      <c r="E81" t="n">
+        <v>0.0634</v>
+      </c>
+      <c r="F81" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>crowd_run_1080p50</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>fastmotion</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>share_entropy_pct</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="E82" t="n">
+        <v>40.3</v>
+      </c>
+      <c r="F82" t="n">
+        <v>-13.9</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>crowd_run_1080p50</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>fastmotion</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>share_inter_mc_pct</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="E83" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="F83" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>crowd_run_1080p50</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>fastmotion</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>share_deblock_pct</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="E84" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="F84" t="n">
+        <v>-8.9</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>crowd_run_1080p50</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>fastmotion</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>ns_per_mb</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>2733.5</v>
+      </c>
+      <c r="E85" t="n">
+        <v>2522.9</v>
+      </c>
+      <c r="F85" t="n">
+        <v>-7.7</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>football_cif</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>fastmotion</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>bits_per_mb</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>135.74</v>
+      </c>
+      <c r="E86" t="n">
+        <v>136.56</v>
+      </c>
+      <c r="F86" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>football_cif</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>fastmotion</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>entropy_calls_per_mb</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>11.31</v>
+      </c>
+      <c r="E87" t="n">
+        <v>7.46</v>
+      </c>
+      <c r="F87" t="n">
+        <v>-34</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>football_cif</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>fastmotion</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>skiprecon_calls_per_mb</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>0.083</v>
+      </c>
+      <c r="E88" t="n">
+        <v>0.091</v>
+      </c>
+      <c r="F88" t="n">
+        <v>9.6</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>football_cif</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>fastmotion</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>dequant_calls_per_mb</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>9.029999999999999</v>
+      </c>
+      <c r="E89" t="n">
+        <v>6.76</v>
+      </c>
+      <c r="F89" t="n">
+        <v>-25.1</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>football_cif</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>fastmotion</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>mc_calls_per_mb</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="E90" t="n">
+        <v>5.18</v>
+      </c>
+      <c r="F90" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>football_cif</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>fastmotion</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>mb_intra_frac</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>0.2184</v>
+      </c>
+      <c r="E91" t="n">
+        <v>0.2207</v>
+      </c>
+      <c r="F91" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>football_cif</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>fastmotion</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>share_entropy_pct</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="E92" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="F92" t="n">
+        <v>-13.1</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>football_cif</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>fastmotion</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>share_inter_mc_pct</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="E93" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="F93" t="n">
+        <v>-3.9</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>football_cif</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>fastmotion</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>share_deblock_pct</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="E94" t="n">
+        <v>5</v>
+      </c>
+      <c r="F94" t="n">
+        <v>-12.3</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>football_cif</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>fastmotion</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>ns_per_mb</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>2571.5</v>
+      </c>
+      <c r="E95" t="n">
+        <v>2668.4</v>
+      </c>
+      <c r="F95" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>foreman_cif</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>bits_per_mb</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>36.17</v>
+      </c>
+      <c r="E96" t="n">
+        <v>37.29</v>
+      </c>
+      <c r="F96" t="n">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>foreman_cif</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>entropy_calls_per_mb</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="E97" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="F97" t="n">
+        <v>-27.7</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>foreman_cif</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>skiprecon_calls_per_mb</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="E98" t="n">
+        <v>0.115</v>
+      </c>
+      <c r="F98" t="n">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>foreman_cif</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>dequant_calls_per_mb</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="E99" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="F99" t="n">
+        <v>-4.2</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>foreman_cif</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>mc_calls_per_mb</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="E100" t="n">
+        <v>5.18</v>
+      </c>
+      <c r="F100" t="n">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>foreman_cif</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>mb_intra_frac</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>0.0267</v>
+      </c>
+      <c r="E101" t="n">
+        <v>0.0276</v>
+      </c>
+      <c r="F101" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>foreman_cif</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>share_entropy_pct</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="E102" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="F102" t="n">
+        <v>-43.9</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>foreman_cif</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>share_inter_mc_pct</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>18</v>
+      </c>
+      <c r="E103" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="F103" t="n">
+        <v>-3.9</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>foreman_cif</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>share_deblock_pct</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>8</v>
+      </c>
+      <c r="E104" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="F104" t="n">
+        <v>-7.5</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>foreman_cif</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>ns_per_mb</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>1475.2</v>
+      </c>
+      <c r="E105" t="n">
+        <v>1380.5</v>
+      </c>
+      <c r="F105" t="n">
+        <v>-6.4</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>grain_akiyo</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>grain</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>bits_per_mb</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>493.25</v>
+      </c>
+      <c r="E106" t="n">
+        <v>520.74</v>
+      </c>
+      <c r="F106" t="n">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>grain_akiyo</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>grain</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>entropy_calls_per_mb</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>25.92</v>
+      </c>
+      <c r="E107" t="n">
+        <v>18.09</v>
+      </c>
+      <c r="F107" t="n">
+        <v>-30.2</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>grain_akiyo</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>grain</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>skiprecon_calls_per_mb</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>0</v>
+      </c>
+      <c r="E108" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>grain_akiyo</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>grain</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>dequant_calls_per_mb</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>23.61</v>
+      </c>
+      <c r="E109" t="n">
+        <v>17.04</v>
+      </c>
+      <c r="F109" t="n">
+        <v>-27.8</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>grain_akiyo</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>grain</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>mc_calls_per_mb</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>5.12</v>
+      </c>
+      <c r="E110" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="F110" t="n">
+        <v>-25.2</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>grain_akiyo</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>grain</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>mb_intra_frac</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>0.3837</v>
+      </c>
+      <c r="E111" t="n">
+        <v>0.5732</v>
+      </c>
+      <c r="F111" t="n">
+        <v>49.4</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>grain_akiyo</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>grain</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>share_entropy_pct</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="E112" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="F112" t="n">
+        <v>-3.8</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>grain_akiyo</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>grain</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>share_inter_mc_pct</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="E113" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="F113" t="n">
+        <v>-27.3</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>grain_akiyo</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>grain</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>share_deblock_pct</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="E114" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="F114" t="n">
+        <v>-19.2</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>grain_akiyo</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>grain</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>ns_per_mb</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>6696.1</v>
+      </c>
+      <c r="E115" t="n">
+        <v>6544.6</v>
+      </c>
+      <c r="F115" t="n">
+        <v>-2.3</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>grain_flat</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>grain</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>bits_per_mb</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>586.91</v>
+      </c>
+      <c r="E116" t="n">
+        <v>580.58</v>
+      </c>
+      <c r="F116" t="n">
+        <v>-1.1</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>grain_flat</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>grain</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>entropy_calls_per_mb</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>26.16</v>
+      </c>
+      <c r="E117" t="n">
+        <v>14.98</v>
+      </c>
+      <c r="F117" t="n">
+        <v>-42.7</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>grain_flat</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>grain</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>skiprecon_calls_per_mb</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>0</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>grain_flat</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>grain</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>dequant_calls_per_mb</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>26.08</v>
+      </c>
+      <c r="E119" t="n">
+        <v>14.97</v>
+      </c>
+      <c r="F119" t="n">
+        <v>-42.6</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>grain_flat</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>grain</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>mc_calls_per_mb</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F120" t="n">
+        <v>-96.40000000000001</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>grain_flat</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>grain</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>mb_intra_frac</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>0.9626</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.9984</v>
+      </c>
+      <c r="F121" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>grain_flat</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>grain</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>share_entropy_pct</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>82.40000000000001</v>
+      </c>
+      <c r="E122" t="n">
+        <v>80.7</v>
+      </c>
+      <c r="F122" t="n">
+        <v>-2.1</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>grain_flat</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>grain</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>share_inter_mc_pct</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0</v>
+      </c>
+      <c r="F123" t="n">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>grain_flat</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>grain</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>share_deblock_pct</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="F124" t="n">
+        <v>-32</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>grain_flat</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>grain</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>ns_per_mb</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>6599.3</v>
+      </c>
+      <c r="E125" t="n">
+        <v>6275.3</v>
+      </c>
+      <c r="F125" t="n">
+        <v>-4.9</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>in_to_tree_420_720p50</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>bits_per_mb</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>20.22</v>
+      </c>
+      <c r="E126" t="n">
+        <v>23.49</v>
+      </c>
+      <c r="F126" t="n">
+        <v>16.2</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>in_to_tree_420_720p50</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>entropy_calls_per_mb</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="E127" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="F127" t="n">
+        <v>-20.9</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>in_to_tree_420_720p50</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>skiprecon_calls_per_mb</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>0.08599999999999999</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.083</v>
+      </c>
+      <c r="F128" t="n">
+        <v>-3.5</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>in_to_tree_420_720p50</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>dequant_calls_per_mb</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="E129" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="F129" t="n">
+        <v>7.9</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>in_to_tree_420_720p50</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>mc_calls_per_mb</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>4</v>
+      </c>
+      <c r="E130" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="F130" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>in_to_tree_420_720p50</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>mb_intra_frac</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>0.0185</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.0234</v>
+      </c>
+      <c r="F131" t="n">
+        <v>26.5</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>in_to_tree_420_720p50</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>share_entropy_pct</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="E132" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="F132" t="n">
+        <v>-10.4</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>in_to_tree_420_720p50</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>share_inter_mc_pct</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="E133" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="F133" t="n">
+        <v>-7.7</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>in_to_tree_420_720p50</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>share_deblock_pct</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="E134" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="F134" t="n">
+        <v>-8.199999999999999</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>in_to_tree_420_720p50</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>ns_per_mb</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>1163.4</v>
+      </c>
+      <c r="E135" t="n">
+        <v>1169.9</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>mobile_cif</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>detail</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>bits_per_mb</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>137.61</v>
+      </c>
+      <c r="E136" t="n">
+        <v>142.6</v>
+      </c>
+      <c r="F136" t="n">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>mobile_cif</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>detail</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>entropy_calls_per_mb</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>10.83</v>
+      </c>
+      <c r="E137" t="n">
+        <v>8.74</v>
+      </c>
+      <c r="F137" t="n">
+        <v>-19.3</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>mobile_cif</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>detail</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>skiprecon_calls_per_mb</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>mobile_cif</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>detail</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>dequant_calls_per_mb</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>6.36</v>
+      </c>
+      <c r="E139" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="F139" t="n">
+        <v>-16.8</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>mobile_cif</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>detail</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>mc_calls_per_mb</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>7.62</v>
+      </c>
+      <c r="E140" t="n">
+        <v>7.65</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>mobile_cif</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>detail</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>mb_intra_frac</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.0105</v>
+      </c>
+      <c r="F141" t="n">
+        <v>-4.5</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>mobile_cif</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>detail</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>share_entropy_pct</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>47.9</v>
+      </c>
+      <c r="E142" t="n">
+        <v>43.8</v>
+      </c>
+      <c r="F142" t="n">
+        <v>-8.6</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>mobile_cif</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>detail</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>share_inter_mc_pct</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>12</v>
+      </c>
+      <c r="E143" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="F143" t="n">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>mobile_cif</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>detail</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>share_deblock_pct</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="E144" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="F144" t="n">
+        <v>-11.5</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>mobile_cif</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>detail</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>ns_per_mb</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>2912.5</v>
+      </c>
+      <c r="E145" t="n">
+        <v>2754.6</v>
+      </c>
+      <c r="F145" t="n">
+        <v>-5.4</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>screen_text</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>screen</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>bits_per_mb</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E146" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="F146" t="n">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>screen_text</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>screen</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>entropy_calls_per_mb</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E147" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F147" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>screen_text</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>screen</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>skiprecon_calls_per_mb</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="E148" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="F148" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>screen_text</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>screen</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>dequant_calls_per_mb</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="E149" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="F149" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>screen_text</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>screen</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>mc_calls_per_mb</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="E150" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="F150" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>screen_text</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>screen</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>mb_intra_frac</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>0.0217</v>
+      </c>
+      <c r="E151" t="n">
+        <v>0.0219</v>
+      </c>
+      <c r="F151" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>screen_text</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>screen</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>share_entropy_pct</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="E152" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="F152" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>screen_text</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>screen</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>share_inter_mc_pct</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="E153" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="F153" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>screen_text</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>screen</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>share_deblock_pct</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="E154" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="F154" t="n">
+        <v>8.300000000000001</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>screen_text</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>screen</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>ns_per_mb</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>534.5</v>
+      </c>
+      <c r="E155" t="n">
+        <v>509.3</v>
+      </c>
+      <c r="F155" t="n">
+        <v>-4.7</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>screen_ui</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>screen</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>bits_per_mb</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>47.13</v>
+      </c>
+      <c r="E156" t="n">
+        <v>47.27</v>
+      </c>
+      <c r="F156" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>screen_ui</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>screen</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>entropy_calls_per_mb</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="E157" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="F157" t="n">
+        <v>-1.9</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>screen_ui</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>screen</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>skiprecon_calls_per_mb</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="E158" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="F158" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>screen_ui</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>screen</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>dequant_calls_per_mb</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="E159" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="F159" t="n">
+        <v>-5.7</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>screen_ui</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>screen</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>mc_calls_per_mb</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="E160" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="F160" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>screen_ui</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>screen</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>mb_intra_frac</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>0.0449</v>
+      </c>
+      <c r="E161" t="n">
+        <v>0.0422</v>
+      </c>
+      <c r="F161" t="n">
+        <v>-6</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>screen_ui</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>screen</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>share_entropy_pct</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="E162" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="F162" t="n">
+        <v>-8.800000000000001</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>screen_ui</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>screen</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>share_inter_mc_pct</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="E163" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="F163" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>screen_ui</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>screen</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>share_deblock_pct</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="E164" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="F164" t="n">
+        <v>-15.6</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>screen_ui</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>screen</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>ns_per_mb</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>1153.2</v>
+      </c>
+      <c r="E165" t="n">
+        <v>1136.4</v>
+      </c>
+      <c r="F165" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>tempete_cif</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>complex</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>bits_per_mb</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>90.64</v>
+      </c>
+      <c r="E166" t="n">
+        <v>94.05</v>
+      </c>
+      <c r="F166" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>tempete_cif</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>complex</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>entropy_calls_per_mb</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="E167" t="n">
+        <v>5.84</v>
+      </c>
+      <c r="F167" t="n">
+        <v>-21.3</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>tempete_cif</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>complex</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>skiprecon_calls_per_mb</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="E168" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="F168" t="n">
+        <v>8.300000000000001</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>tempete_cif</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>complex</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>dequant_calls_per_mb</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="E169" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="F169" t="n">
+        <v>-14.9</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>tempete_cif</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>complex</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>mc_calls_per_mb</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="E170" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="F170" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>tempete_cif</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>complex</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>mb_intra_frac</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>0.0172</v>
+      </c>
+      <c r="E171" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="F171" t="n">
+        <v>-4.1</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>tempete_cif</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>complex</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>share_entropy_pct</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>40.2</v>
+      </c>
+      <c r="E172" t="n">
+        <v>36.2</v>
+      </c>
+      <c r="F172" t="n">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>tempete_cif</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>complex</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>share_inter_mc_pct</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="E173" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="F173" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>tempete_cif</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>complex</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>share_deblock_pct</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>7</v>
+      </c>
+      <c r="E174" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="F174" t="n">
+        <v>-11.4</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>tempete_cif</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>complex</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>ns_per_mb</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>2262.2</v>
+      </c>
+      <c r="E175" t="n">
+        <v>2148.6</v>
+      </c>
+      <c r="F175" t="n">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="3" t="inlineStr">
+        <is>
+          <t>GATE 1 routing under the v1 MAIN tree</t>
+        </is>
+      </c>
+      <c r="B177" s="3" t="inlineStr"/>
+      <c r="C177" s="3" t="inlineStr"/>
+      <c r="D177" s="3" t="inlineStr">
+        <is>
+          <t>MAIN route</t>
+        </is>
+      </c>
+      <c r="E177" s="3" t="inlineStr">
+        <is>
+          <t>DEFAULT route</t>
+        </is>
+      </c>
+      <c r="F177" s="3" t="inlineStr">
+        <is>
+          <t>changed?</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>720p50_shields_ter</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>detail</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>truth=DENSE-INTER</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>DENSE-INTER</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>720p5994_stockholm_ter</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>pan</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>truth=DENSE-INTER</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>DENSE-INTER</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>FourPeople_1280x720_60</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>static</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>truth=LIGHT</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>LIGHT</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>LIGHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>akiyo_cif</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>static</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>truth=LIGHT</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>LIGHT</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>LIGHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>blue_sky_1080p25</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>smooth</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>truth=MID</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>bus_cif</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>pan</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>truth=DENSE-INTER</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>DENSE-INTER</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>DENSE-INTER</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>crew_4cif</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>complex</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>truth=DENSE-INTER</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>DENSE-INTER</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>crowd_run_1080p50</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>fastmotion</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>truth=DENSE-INTER</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>DENSE-INTER</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>DENSE-INTER</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>football_cif</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>fastmotion</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>truth=DENSE-INTER</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>DENSE-INTER</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>DENSE-INTER</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>foreman_cif</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>truth=MID</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>grain_akiyo</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>grain</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>truth=ENTROPY-EXTREME</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>ENTROPY-EXTREME</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>ENTROPY-EXTREME</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>grain_flat</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>grain</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>truth=ENTROPY-EXTREME</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>ENTROPY-EXTREME</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>ENTROPY-EXTREME</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>in_to_tree_420_720p50</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>truth=MID</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>mobile_cif</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>detail</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>truth=DENSE-INTER</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>DENSE-INTER</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>DENSE-INTER</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>screen_text</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>screen</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>truth=LIGHT</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>LIGHT</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>LIGHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>screen_ui</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>screen</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>truth=LIGHT</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>LIGHT</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>LIGHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>tempete_cif</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>complex</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>truth=DENSE-INTER</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>DENSE-INTER</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>DENSE-INTER</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="1" t="inlineStr">
+        <is>
+          <t>summary</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>v1-tree errors on MAIN: 0/17</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>on DEFAULT: 3/17</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>routes changed: 3/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="1" t="inlineStr">
+        <is>
+          <t>TREE TRANSFER CHECK on DEFAULT streams</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>main-tree (root 3.575)</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>3/17 errors — shields/stockholm/crew fall below the Main-profile root into MID (8x8 transform lowers entropy_calls_per_mb)</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>high-tree (root 2.335)</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>1/17 errors (screen_ui LIGHT-&gt;MID) — default's distribution sits at the HIGH end of the bracket; use high-tree thresholds as v2 seed for default-MAIN, then refit</t>
         </is>
       </c>
     </row>

--- a/docs/big-oppy-decoder-truthtable.xlsx
+++ b/docs/big-oppy-decoder-truthtable.xlsx
@@ -13,6 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="gate_fit" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="gate_fit_per_tier" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="main_vs_default" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="vs_ffmpeg_default" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -14409,4 +14410,409 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ours vs ffmpeg, SAME x264-default streams; concat &gt;=800ms, frames verified, best-of-3 alternating; loaded box — ratio robust</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>class</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>clip</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>ours ns/MB</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>ffmpeg ns/MB</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>static</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>FourPeople_1280x720_60</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>890</v>
+      </c>
+      <c r="D3" t="n">
+        <v>289</v>
+      </c>
+      <c r="E3" t="n">
+        <v>3.08</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>static</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>akiyo_cif</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>878</v>
+      </c>
+      <c r="D4" t="n">
+        <v>267</v>
+      </c>
+      <c r="E4" t="n">
+        <v>3.29</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>foreman_cif</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1681</v>
+      </c>
+      <c r="D5" t="n">
+        <v>804</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2.09</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>in_to_tree_420_720p50</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1431</v>
+      </c>
+      <c r="D6" t="n">
+        <v>603</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2.37</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>detail</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>720p50_shields_ter</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1669</v>
+      </c>
+      <c r="D7" t="n">
+        <v>796</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>detail</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>mobile_cif</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>3309</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1776</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1.86</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>pan</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>720p5994_stockholm_ter</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1733</v>
+      </c>
+      <c r="D9" t="n">
+        <v>819</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2.11</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>pan</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>bus_cif</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>2830</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1536</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.84</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>complex</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>crew_4cif</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1705</v>
+      </c>
+      <c r="D11" t="n">
+        <v>768</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2.22</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>complex</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>tempete_cif</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>2758</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1424</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1.94</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>fastmotion</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>crowd_run_1080p50</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>3057</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1565</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1.95</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>fastmotion</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>football_cif</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>3111</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1698</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1.83</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>smooth</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>blue_sky_1080p25</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1343</v>
+      </c>
+      <c r="D15" t="n">
+        <v>559</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>grain</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>grain_akiyo</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>7462</v>
+      </c>
+      <c r="D16" t="n">
+        <v>4935</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1.51</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>grain</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>grain_flat</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>7292</v>
+      </c>
+      <c r="D17" t="n">
+        <v>5126</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>screen</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>screen_text</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>631</v>
+      </c>
+      <c r="D18" t="n">
+        <v>227</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2.78</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>screen</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>screen_ui</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1448</v>
+      </c>
+      <c r="D19" t="n">
+        <v>686</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2.11</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/big-oppy-decoder-truthtable.xlsx
+++ b/docs/big-oppy-decoder-truthtable.xlsx
@@ -14,6 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="gate_fit_per_tier" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="main_vs_default" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="vs_ffmpeg_default" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="vs_ffmpeg_default_0821" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -14815,4 +14816,623 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>RE-BASELINE 2026-08-21 of the vs_ffmpeg_default sheet, whose timings were loaded-box / ORDINAL-ONLY.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>protocol</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>x264-default streams; concat past 1500 ms; frame-count parity per clip; pinned 1-core CPU time; ffmpeg -threads 1 -f null; 7 ABBA pairs; median per arm; ns/MB = median CPU / MBs decoded</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>identical harness re-run on the 2026-08-19 binary deb416b (same --features asm) so decoder gains separate from box/protocol; ffmpeg column is the control</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>build</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>HEAD b3368bd (batch 10), --features asm; ymm-verified accel</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>class</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>clip</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ours ns/MB</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>ffmpeg ns/MB</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>ours ns/MB @08-19</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>ours change</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>frames timed</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>static</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>FourPeople_1280x720_60</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>568</v>
+      </c>
+      <c r="D7" t="n">
+        <v>323</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="F7" t="n">
+        <v>796</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-0.2864</v>
+      </c>
+      <c r="H7" t="n">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>static</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>akiyo_cif</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>555</v>
+      </c>
+      <c r="D8" t="n">
+        <v>375</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="F8" t="n">
+        <v>780</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-0.2885</v>
+      </c>
+      <c r="H8" t="n">
+        <v>7680</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>foreman_cif</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1487</v>
+      </c>
+      <c r="D9" t="n">
+        <v>940</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1550</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-0.0406</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2520</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>in_to_tree_420_720p50</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1209</v>
+      </c>
+      <c r="D10" t="n">
+        <v>641</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1290</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-0.06279999999999999</v>
+      </c>
+      <c r="H10" t="n">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>detail</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>720p50_shields_ter</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1432</v>
+      </c>
+      <c r="D11" t="n">
+        <v>795</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1577</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-0.0919</v>
+      </c>
+      <c r="H11" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>detail</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>mobile_cif</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1913</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="F12" t="n">
+        <v>3109</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-0.0672</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>pan</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>720p5994_stockholm_ter</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>1548</v>
+      </c>
+      <c r="D13" t="n">
+        <v>825</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1721</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-0.1005</v>
+      </c>
+      <c r="H13" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>pan</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>bus_cif</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>2419</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1598</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2605</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-0.07140000000000001</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1680</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>complex</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>crew_4cif</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1425</v>
+      </c>
+      <c r="D15" t="n">
+        <v>808</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1645</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-0.1337</v>
+      </c>
+      <c r="H15" t="n">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>complex</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>tempete_cif</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>2346</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1469</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2554</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-0.0814</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>fastmotion</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>crowd_run_1080p50</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>2749</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1655</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2846</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-0.0341</v>
+      </c>
+      <c r="H17" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>fastmotion</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>football_cif</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>2741</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1808</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="F18" t="n">
+        <v>3206</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-0.145</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>smooth</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>blue_sky_1080p25</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1126</v>
+      </c>
+      <c r="D19" t="n">
+        <v>579</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1211</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-0.0702</v>
+      </c>
+      <c r="H19" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>grain</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>grain_akiyo</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>6772</v>
+      </c>
+      <c r="D20" t="n">
+        <v>4802</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="F20" t="n">
+        <v>6772</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>grain</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>grain_flat</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>6709</v>
+      </c>
+      <c r="D21" t="n">
+        <v>5063</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="F21" t="n">
+        <v>6641</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.0102</v>
+      </c>
+      <c r="H21" t="n">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>screen</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>screen_text</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>285</v>
+      </c>
+      <c r="D22" t="n">
+        <v>243</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="F22" t="n">
+        <v>571</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-0.5009</v>
+      </c>
+      <c r="H22" t="n">
+        <v>14100</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>screen</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>screen_ui</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1039</v>
+      </c>
+      <c r="D23" t="n">
+        <v>711</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1193</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-0.1291</v>
+      </c>
+      <c r="H23" t="n">
+        <v>3720</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>